--- a/data.mn/public/datasets/nso-foreign-trade-monthly.xlsx
+++ b/data.mn/public/datasets/nso-foreign-trade-monthly.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -7108,16 +7108,16 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>939.52</v>
+        <v>939.76</v>
       </c>
       <c r="C352" t="n">
-        <v>1842.83</v>
+        <v>1842.77</v>
       </c>
       <c r="D352" t="n">
-        <v>903.3099999999999</v>
+        <v>903</v>
       </c>
       <c r="E352" t="n">
-        <v>2746.14</v>
+        <v>2745.77</v>
       </c>
     </row>
     <row r="353">
@@ -7127,16 +7127,16 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>735.39</v>
+        <v>735.41</v>
       </c>
       <c r="C353" t="n">
         <v>1923.81</v>
       </c>
       <c r="D353" t="n">
-        <v>1188.42</v>
+        <v>1188.4</v>
       </c>
       <c r="E353" t="n">
-        <v>3112.23</v>
+        <v>3112.21</v>
       </c>
     </row>
     <row r="354">
@@ -7146,16 +7146,16 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>447.72</v>
+        <v>447.78</v>
       </c>
       <c r="C354" t="n">
         <v>1657.46</v>
       </c>
       <c r="D354" t="n">
-        <v>1209.74</v>
+        <v>1209.68</v>
       </c>
       <c r="E354" t="n">
-        <v>2867.21</v>
+        <v>2867.14</v>
       </c>
     </row>
     <row r="355">
@@ -7165,16 +7165,16 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>687.65</v>
+        <v>687.89</v>
       </c>
       <c r="C355" t="n">
         <v>1923.38</v>
       </c>
       <c r="D355" t="n">
-        <v>1235.73</v>
+        <v>1235.49</v>
       </c>
       <c r="E355" t="n">
-        <v>3159.12</v>
+        <v>3158.86</v>
       </c>
     </row>
     <row r="356">
@@ -7184,16 +7184,54 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>766.97</v>
+        <v>768.2</v>
       </c>
       <c r="C356" t="n">
-        <v>1812.04</v>
+        <v>1812</v>
       </c>
       <c r="D356" t="n">
-        <v>1045.07</v>
+        <v>1043.8</v>
       </c>
       <c r="E356" t="n">
-        <v>2857.11</v>
+        <v>2855.81</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>979.2</v>
+      </c>
+      <c r="C357" t="n">
+        <v>2188.7</v>
+      </c>
+      <c r="D357" t="n">
+        <v>1209.5</v>
+      </c>
+      <c r="E357" t="n">
+        <v>3398.2</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>444.76</v>
+      </c>
+      <c r="C358" t="n">
+        <v>1804.07</v>
+      </c>
+      <c r="D358" t="n">
+        <v>1359.31</v>
+      </c>
+      <c r="E358" t="n">
+        <v>3163.39</v>
       </c>
     </row>
   </sheetData>
@@ -7207,14 +7245,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:E358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13901,16 +13939,16 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>903.3099999999999</v>
+        <v>903</v>
       </c>
       <c r="C352" t="n">
-        <v>2746.14</v>
+        <v>2745.77</v>
       </c>
       <c r="D352" t="n">
-        <v>939.52</v>
+        <v>939.76</v>
       </c>
       <c r="E352" t="n">
-        <v>1842.83</v>
+        <v>1842.77</v>
       </c>
     </row>
     <row r="353">
@@ -13920,13 +13958,13 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1188.42</v>
+        <v>1188.4</v>
       </c>
       <c r="C353" t="n">
-        <v>3112.23</v>
+        <v>3112.21</v>
       </c>
       <c r="D353" t="n">
-        <v>735.39</v>
+        <v>735.41</v>
       </c>
       <c r="E353" t="n">
         <v>1923.81</v>
@@ -13939,13 +13977,13 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>1209.74</v>
+        <v>1209.68</v>
       </c>
       <c r="C354" t="n">
-        <v>2867.21</v>
+        <v>2867.14</v>
       </c>
       <c r="D354" t="n">
-        <v>447.72</v>
+        <v>447.78</v>
       </c>
       <c r="E354" t="n">
         <v>1657.46</v>
@@ -13958,13 +13996,13 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>1235.73</v>
+        <v>1235.49</v>
       </c>
       <c r="C355" t="n">
-        <v>3159.12</v>
+        <v>3158.86</v>
       </c>
       <c r="D355" t="n">
-        <v>687.65</v>
+        <v>687.89</v>
       </c>
       <c r="E355" t="n">
         <v>1923.38</v>
@@ -13977,16 +14015,54 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>1045.07</v>
+        <v>1043.8</v>
       </c>
       <c r="C356" t="n">
-        <v>2857.11</v>
+        <v>2855.81</v>
       </c>
       <c r="D356" t="n">
-        <v>766.97</v>
+        <v>768.2</v>
       </c>
       <c r="E356" t="n">
-        <v>1812.04</v>
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>1209.5</v>
+      </c>
+      <c r="C357" t="n">
+        <v>3398.2</v>
+      </c>
+      <c r="D357" t="n">
+        <v>979.2</v>
+      </c>
+      <c r="E357" t="n">
+        <v>2188.7</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>1359.31</v>
+      </c>
+      <c r="C358" t="n">
+        <v>3163.39</v>
+      </c>
+      <c r="D358" t="n">
+        <v>444.76</v>
+      </c>
+      <c r="E358" t="n">
+        <v>1804.07</v>
       </c>
     </row>
   </sheetData>
